--- a/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 15,48</t>
+          <t>-14,59; 14,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 15,9</t>
+          <t>-14,89; 15,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 0,0</t>
+          <t>-37,27; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 0,0</t>
+          <t>-35,44; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 7,65</t>
+          <t>-12,19; 8,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 9,78</t>
+          <t>-6,02; 10,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 8,04</t>
+          <t>-10,21; 7,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 4,35</t>
+          <t>-10,39; 5,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 48,83</t>
+          <t>-47,12; 59,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 117,15</t>
+          <t>-38,01; 129,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 66,19</t>
+          <t>-49,72; 68,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 56,04</t>
+          <t>-70,72; 66,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 9,76</t>
+          <t>-17,19; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 7,18</t>
+          <t>-18,8; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 23,34</t>
+          <t>-7,17; 21,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 13,31</t>
+          <t>-7,09; 15,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 180,61</t>
+          <t>-100,0; 221,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,92; 115,77</t>
+          <t>-83,43; 92,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 589,19</t>
+          <t>-59,39; 670,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,19; 399,21</t>
+          <t>-69,25; 485,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 6,47</t>
+          <t>-7,54; 6,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 5,91</t>
+          <t>-6,68; 6,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,46</t>
+          <t>-8,45; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,64</t>
+          <t>-8,19; 3,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 46,46</t>
+          <t>-39,64; 46,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 62,87</t>
+          <t>-42,51; 62,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 55,84</t>
+          <t>-43,91; 70,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 50,59</t>
+          <t>-62,8; 52,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 14,21</t>
+          <t>-14,95; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 15,21</t>
+          <t>-13,95; 15,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 0,0</t>
+          <t>-36,55; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 0,0</t>
+          <t>-38,13; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 8,8</t>
+          <t>-11,65; 8,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 10,58</t>
+          <t>-6,42; 9,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 7,94</t>
+          <t>-11,05; 7,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 5,4</t>
+          <t>-10,62; 5,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 59,9</t>
+          <t>-46,05; 56,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 129,25</t>
+          <t>-42,5; 115,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 68,75</t>
+          <t>-51,06; 61,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 66,5</t>
+          <t>-71,53; 65,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 9,96</t>
+          <t>-15,85; 9,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 5,94</t>
+          <t>-19,53; 6,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 21,46</t>
+          <t>-8,81; 20,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 15,02</t>
+          <t>-6,55; 14,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,52</t>
+          <t>-100,0; 224,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,43; 92,67</t>
+          <t>-83,48; 114,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 670,67</t>
+          <t>-73,32; 593,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 485,88</t>
+          <t>-65,24; 427,33</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 6,05</t>
+          <t>-7,99; 6,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,09</t>
+          <t>-6,75; 5,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,19</t>
+          <t>-8,06; 5,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,95</t>
+          <t>-7,72; 3,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 46,89</t>
+          <t>-41,19; 54,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 62,47</t>
+          <t>-42,07; 60,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 70,67</t>
+          <t>-44,31; 55,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 52,54</t>
+          <t>-58,5; 51,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-10,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 14,59</t>
+          <t>-13,08; 15,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 15,73</t>
+          <t>-13,97; 15,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 0,0</t>
+          <t>-40,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 0,0</t>
+          <t>-37,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,79%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 8,74</t>
+          <t>-11,99; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 9,98</t>
+          <t>-6,96; 9,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 7,27</t>
+          <t>-11,47; 8,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 5,18</t>
+          <t>-8,48; 7,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,05; 56,97</t>
+          <t>-48,29; 48,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 115,17</t>
+          <t>-43,14; 117,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 61,93</t>
+          <t>-52,66; 66,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 65,13</t>
+          <t>-54,38; 96,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>4,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 9,67</t>
+          <t>-16,82; 9,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 6,18</t>
+          <t>-19,44; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 20,17</t>
+          <t>-6,57; 23,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 14,31</t>
+          <t>-6,73; 14,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,95</t>
+          <t>-100,0; 180,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,48; 114,79</t>
+          <t>-82,92; 115,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,32; 593,22</t>
+          <t>-66,43; 589,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 427,33</t>
+          <t>-70,65; 449,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 6,93</t>
+          <t>-8,19; 6,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,7</t>
+          <t>-6,53; 5,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,69</t>
+          <t>-8,12; 6,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,87</t>
+          <t>-6,03; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 54,92</t>
+          <t>-40,32; 46,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 60,27</t>
+          <t>-42,57; 62,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 55,02</t>
+          <t>-46,22; 55,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 51,23</t>
+          <t>-46,01; 89,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.2936010646129569</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7615109854166385</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.152981035773067</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.661248094018453</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1533481155444433</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.479650680514161</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; 15,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,97; 15,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-40,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-37,78; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.929852016664981</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.363202052295849</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.682902169935169</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.192133401607174</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.62463865940428</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.911448424290107</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-9,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,99; 7,65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; 9,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,47; 8,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,48; 7,45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-48,29; 48,83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,14; 117,15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-52,66; 66,19</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-54,38; 96,03</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.0676789979098473</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1565675793700171</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2636543924774592</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.1167411820898762</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01873477029464365</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06141395540517814</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.08734843783266684</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04547904461311034</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,73</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-29,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-40,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54,84%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.960196581716426</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.56837004903409</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.107546027480345</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.102762904523913</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.441408417778276</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4521402176100135</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5385762554458065</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6091254252438278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-16,82; 9,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,44; 7,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,57; 23,34</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 14,98</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 180,61</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-82,92; 115,77</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-66,43; 589,19</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-70,65; 449,12</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.142210902897915</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.940297999530595</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.521756246642761</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.779268993810585</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7843629124691691</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.072775282036599</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.74782009082997</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.109381196393551</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +803,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-6,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.680515065689757</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.545610928535371</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.213918565315358</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.27231578855429</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5883728181283226</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4339971351625727</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.8331855002788366</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.6342622642185085</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 6,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,53; 5,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,12; 6,46</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 6,56</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-40,32; 46,46</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-42,57; 62,87</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-46,22; 55,84</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-46,01; 89,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.534117140677689</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.820154763179023</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.015200203280232</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.577697256545742</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8248330646492482</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6366164307974769</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6274822693134894</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6660114147926035</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.218392198706255</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.215138302419128</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.720240745570139</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.103759399711412</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.9407354050877189</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>6.039596511902656</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5.286197050754059</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.398968192420357</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1719990475128799</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04844959860439597</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.0292724479557728</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1230397396815802</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06442220517478699</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01974695493197374</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.0119986570438919</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.774409728332801</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.572821918711955</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.457243137778523</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.600165073470975</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.460357650084266</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4781946647921508</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4452118627030113</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4939032881108182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.128656719362975</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.338851257323747</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.545906819941361</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.560698385661708</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4756062628287079</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7414891677318004</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.878297629535423</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9332112705907994</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1001,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
